--- a/inputs/slope/input_template_griffiths1_6.xlsx
+++ b/inputs/slope/input_template_griffiths1_6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/cursor_projects/xslope/inputs/slope/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67E3E95-0D2F-954C-9370-B0C3742FF953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0936D3-AC1D-7745-ADF3-3CA4685F085C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34080" yWindow="3440" windowWidth="36380" windowHeight="18420" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="32240" yWindow="3440" windowWidth="36380" windowHeight="18420" activeTab="3" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -6413,7 +6413,7 @@
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
-      <c r="W4" s="3">
+      <c r="W4" s="1">
         <v>700000</v>
       </c>
       <c r="X4" s="3">
@@ -6728,7 +6728,7 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" t="s">
         <v>59</v>
       </c>
@@ -6738,9 +6738,8 @@
       <c r="K18" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="W18" s="5"/>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="24" t="s">
         <v>85</v>
       </c>
@@ -6759,7 +6758,7 @@
       <c r="P19" s="44"/>
       <c r="Q19" s="44"/>
     </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20"/>
       <c r="D20"/>
       <c r="E20"/>
@@ -6776,7 +6775,7 @@
       <c r="P20" s="44"/>
       <c r="Q20" s="44"/>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="6" t="s">
         <v>69</v>
       </c>
@@ -6793,7 +6792,7 @@
       <c r="P21" s="44"/>
       <c r="Q21" s="44"/>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>68</v>
       </c>
@@ -6803,7 +6802,7 @@
       <c r="E22"/>
       <c r="F22"/>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>71</v>
       </c>
@@ -6813,13 +6812,13 @@
       <c r="E23"/>
       <c r="F23"/>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24"/>
       <c r="F24"/>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="6" t="s">
         <v>99</v>
       </c>
@@ -6827,7 +6826,7 @@
       <c r="E25"/>
       <c r="F25"/>
     </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>102</v>
       </c>
@@ -6837,7 +6836,7 @@
       <c r="E26"/>
       <c r="F26"/>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
@@ -6847,7 +6846,7 @@
       <c r="E27"/>
       <c r="F27"/>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>103</v>
       </c>

--- a/inputs/slope/input_template_griffiths1_6.xlsx
+++ b/inputs/slope/input_template_griffiths1_6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/cursor_projects/xslope/inputs/slope/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0936D3-AC1D-7745-ADF3-3CA4685F085C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3645DF27-2956-2642-AD26-83DB99DC405B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32240" yWindow="3440" windowWidth="36380" windowHeight="18420" activeTab="3" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="33040" yWindow="1360" windowWidth="34660" windowHeight="19780" activeTab="3" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -859,7 +859,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -992,6 +992,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -6413,11 +6416,11 @@
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
-      <c r="W4" s="1">
+      <c r="W4" s="50">
         <v>700000</v>
       </c>
       <c r="X4" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.2">

--- a/inputs/slope/input_template_griffiths1_6.xlsx
+++ b/inputs/slope/input_template_griffiths1_6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/cursor_projects/xslope/inputs/slope/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3645DF27-2956-2642-AD26-83DB99DC405B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D73E5FF-D079-8D47-A1DE-9C0E17D23B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33040" yWindow="1360" windowWidth="34660" windowHeight="19780" activeTab="3" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="32840" yWindow="4060" windowWidth="34660" windowHeight="19780" activeTab="3" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
